--- a/up.xlsx
+++ b/up.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:J74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,6 +423,15 @@
         <v>volume</v>
       </c>
       <c r="G1" t="str">
+        <v>200 DMA</v>
+      </c>
+      <c r="H1" t="str">
+        <v>EMA10</v>
+      </c>
+      <c r="I1" t="str">
+        <v>SMA50</v>
+      </c>
+      <c r="J1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -431,21 +440,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Pnb Housing Finance Limited</v>
+        <v>Tech Mahindra Limited</v>
       </c>
       <c r="C2" t="str">
-        <v>PNBHOUSING</v>
+        <v>TECHM</v>
       </c>
       <c r="D2" s="1">
-        <v>1200.3</v>
+        <v>1543.5</v>
       </c>
       <c r="E2" s="2">
-        <v>3.65</v>
+        <v>4.93</v>
       </c>
       <c r="F2" s="1">
-        <v>601702</v>
-      </c>
-      <c r="G2" t="str">
+        <v>3097866</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1517.05</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1516.05</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1575.62</v>
+      </c>
+      <c r="J2" t="str">
         <v/>
       </c>
     </row>
@@ -454,21 +472,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Angel One Ltd</v>
+        <v>Mphasis Limited</v>
       </c>
       <c r="C3" t="str">
-        <v>ANGELONE</v>
+        <v>MPHASIS</v>
       </c>
       <c r="D3" s="1">
-        <v>302.2</v>
+        <v>2466.3</v>
       </c>
       <c r="E3" s="2">
-        <v>3.49</v>
+        <v>4.79</v>
       </c>
       <c r="F3" s="1">
-        <v>2969372</v>
-      </c>
-      <c r="G3" t="str">
+        <v>1097687</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2391.05</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2329.8</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2377.74</v>
+      </c>
+      <c r="J3" t="str">
         <v/>
       </c>
     </row>
@@ -477,21 +504,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Siemens Limited</v>
+        <v>Ujjivan Small Finance Bank Ltd</v>
       </c>
       <c r="C4" t="str">
-        <v>SIEMENS</v>
+        <v>UJJIVANSFB</v>
       </c>
       <c r="D4" s="1">
-        <v>3704.7</v>
+        <v>65.25</v>
       </c>
       <c r="E4" s="2">
-        <v>3.05</v>
+        <v>4.65</v>
       </c>
       <c r="F4" s="1">
-        <v>99287</v>
-      </c>
-      <c r="G4" t="str">
+        <v>17186979</v>
+      </c>
+      <c r="G4" s="1">
+        <v>60.75</v>
+      </c>
+      <c r="H4" s="1">
+        <v>64.09</v>
+      </c>
+      <c r="I4" s="1">
+        <v>67.13</v>
+      </c>
+      <c r="J4" t="str">
         <v/>
       </c>
     </row>
@@ -500,21 +536,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Abb India Limited</v>
+        <v>Coforge (Niit Tech) Ltd</v>
       </c>
       <c r="C5" t="str">
-        <v>ABB</v>
+        <v>COFORGE</v>
       </c>
       <c r="D5" s="1">
-        <v>6956</v>
+        <v>1929</v>
       </c>
       <c r="E5" s="2">
-        <v>2.6</v>
+        <v>4.46</v>
       </c>
       <c r="F5" s="1">
-        <v>79378</v>
-      </c>
-      <c r="G5" t="str">
+        <v>3772375</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1524.69</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1845.47</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1842.69</v>
+      </c>
+      <c r="J5" t="str">
         <v/>
       </c>
     </row>
@@ -523,21 +568,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Polycab India Ltd</v>
+        <v>Prestige Estates Projects Limited</v>
       </c>
       <c r="C6" t="str">
-        <v>POLYCAB</v>
+        <v>PRESTIGE</v>
       </c>
       <c r="D6" s="1">
-        <v>8458.5</v>
+        <v>1485</v>
       </c>
       <c r="E6" s="2">
-        <v>2.47</v>
+        <v>3.88</v>
       </c>
       <c r="F6" s="1">
-        <v>184170</v>
-      </c>
-      <c r="G6" t="str">
+        <v>393413</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1479.83</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1449.27</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1535.74</v>
+      </c>
+      <c r="J6" t="str">
         <v/>
       </c>
     </row>
@@ -546,21 +600,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Motilal Oswal Financial Services Limited</v>
+        <v>Persistent Systems Limited</v>
       </c>
       <c r="C7" t="str">
-        <v>MOTILALOFS</v>
+        <v>PERSISTENT</v>
       </c>
       <c r="D7" s="1">
-        <v>1050</v>
+        <v>5988</v>
       </c>
       <c r="E7" s="2">
-        <v>2.34</v>
+        <v>3.47</v>
       </c>
       <c r="F7" s="1">
-        <v>313210</v>
-      </c>
-      <c r="G7" t="str">
+        <v>1003770</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5353.68</v>
+      </c>
+      <c r="H7" s="1">
+        <v>5624.8</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5531.9</v>
+      </c>
+      <c r="J7" t="str">
         <v/>
       </c>
     </row>
@@ -569,21 +632,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Hitachi Energy India Ltd</v>
+        <v>The Phoenix Mills Limited</v>
       </c>
       <c r="C8" t="str">
-        <v>POWERINDIA</v>
+        <v>PHOENIXLTD</v>
       </c>
       <c r="D8" s="1">
-        <v>31315</v>
+        <v>1902.6</v>
       </c>
       <c r="E8" s="2">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="F8" s="1">
-        <v>30986</v>
-      </c>
-      <c r="G8" t="str">
+        <v>572164</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1822.87</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1873.08</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1909.34</v>
+      </c>
+      <c r="J8" t="str">
         <v/>
       </c>
     </row>
@@ -592,21 +664,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Hindustan Aeronautics Ltd</v>
+        <v>Bajaj Auto Limited</v>
       </c>
       <c r="C9" t="str">
-        <v>HAL</v>
+        <v>BAJAJ-AUTO</v>
       </c>
       <c r="D9" s="1">
-        <v>4758.5</v>
+        <v>10318</v>
       </c>
       <c r="E9" s="2">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="F9" s="1">
-        <v>125189</v>
-      </c>
-      <c r="G9" t="str">
+        <v>332152</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10235.32</v>
+      </c>
+      <c r="H9" s="1">
+        <v>10234.06</v>
+      </c>
+      <c r="I9" s="1">
+        <v>11378.94</v>
+      </c>
+      <c r="J9" t="str">
         <v/>
       </c>
     </row>
@@ -615,21 +696,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Ujjivan Small Finance Bank Ltd</v>
+        <v>Sagility India Ltd</v>
       </c>
       <c r="C10" t="str">
-        <v>UJJIVANSFB</v>
+        <v>SAGILITY</v>
       </c>
       <c r="D10" s="1">
-        <v>62.64</v>
+        <v>44.36</v>
       </c>
       <c r="E10" s="2">
-        <v>1.94</v>
+        <v>2.71</v>
       </c>
       <c r="F10" s="1">
-        <v>8107061</v>
-      </c>
-      <c r="G10" t="str">
+        <v>12661539</v>
+      </c>
+      <c r="G10" s="1">
+        <v>43.85</v>
+      </c>
+      <c r="H10" s="1">
+        <v>43.72</v>
+      </c>
+      <c r="I10" s="1">
+        <v>44.25</v>
+      </c>
+      <c r="J10" t="str">
         <v/>
       </c>
     </row>
@@ -638,21 +728,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Apl Apollo Tubes Limited</v>
+        <v>Oracle Financial Services Software Limited</v>
       </c>
       <c r="C11" t="str">
-        <v>APLAPOLLO</v>
+        <v>OFSS</v>
       </c>
       <c r="D11" s="1">
-        <v>2152.9</v>
+        <v>10640</v>
       </c>
       <c r="E11" s="2">
-        <v>1.84</v>
+        <v>2.7</v>
       </c>
       <c r="F11" s="1">
-        <v>67227</v>
-      </c>
-      <c r="G11" t="str">
+        <v>341460</v>
+      </c>
+      <c r="G11" s="1">
+        <v>9320.85</v>
+      </c>
+      <c r="H11" s="1">
+        <v>10582.62</v>
+      </c>
+      <c r="I11" s="1">
+        <v>11431.52</v>
+      </c>
+      <c r="J11" t="str">
         <v/>
       </c>
     </row>
@@ -661,21 +760,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>GE Vernova T&amp;D India Ltd</v>
+        <v>Bajaj Finance Limited</v>
       </c>
       <c r="C12" t="str">
-        <v>GVT&amp;D</v>
+        <v>BAJFINANCE</v>
       </c>
       <c r="D12" s="1">
-        <v>4271.3</v>
+        <v>982.75</v>
       </c>
       <c r="E12" s="2">
-        <v>1.83</v>
+        <v>2.66</v>
       </c>
       <c r="F12" s="1">
-        <v>78716</v>
-      </c>
-      <c r="G12" t="str">
+        <v>7319045</v>
+      </c>
+      <c r="G12" s="1">
+        <v>975.43</v>
+      </c>
+      <c r="H12" s="1">
+        <v>971.18</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1045.34</v>
+      </c>
+      <c r="J12" t="str">
         <v/>
       </c>
     </row>
@@ -684,21 +792,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Tvs Motor Company Limited</v>
+        <v>Trent Limited</v>
       </c>
       <c r="C13" t="str">
-        <v>TVSMOTOR</v>
+        <v>TRENT</v>
       </c>
       <c r="D13" s="1">
-        <v>3937.4</v>
+        <v>2987.8</v>
       </c>
       <c r="E13" s="2">
-        <v>1.83</v>
+        <v>2.57</v>
       </c>
       <c r="F13" s="1">
-        <v>261706</v>
-      </c>
-      <c r="G13" t="str">
+        <v>858762</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2779.67</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2845.5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2866.38</v>
+      </c>
+      <c r="J13" t="str">
         <v/>
       </c>
     </row>
@@ -707,21 +824,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Ather Energy Ltd</v>
+        <v>Angel One Ltd</v>
       </c>
       <c r="C14" t="str">
-        <v>ATHERENERG</v>
+        <v>ANGELONE</v>
       </c>
       <c r="D14" s="1">
-        <v>1456.5</v>
+        <v>310</v>
       </c>
       <c r="E14" s="2">
-        <v>1.54</v>
+        <v>2.56</v>
       </c>
       <c r="F14" s="1">
-        <v>1389407</v>
-      </c>
-      <c r="G14" t="str">
+        <v>6591557</v>
+      </c>
+      <c r="G14" s="1">
+        <v>288.28</v>
+      </c>
+      <c r="H14" s="1">
+        <v>295.8</v>
+      </c>
+      <c r="I14" s="1">
+        <v>293.03</v>
+      </c>
+      <c r="J14" t="str">
         <v/>
       </c>
     </row>
@@ -730,21 +856,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Manappuram Finance Limited</v>
+        <v>Adani Enterprises Limited</v>
       </c>
       <c r="C15" t="str">
-        <v>MANAPPURAM</v>
+        <v>ADANIENT</v>
       </c>
       <c r="D15" s="1">
-        <v>319.3</v>
+        <v>2695</v>
       </c>
       <c r="E15" s="2">
-        <v>1.43</v>
+        <v>2.47</v>
       </c>
       <c r="F15" s="1">
-        <v>1679234</v>
-      </c>
-      <c r="G15" t="str">
+        <v>1187944</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2583.24</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2745.37</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2949.28</v>
+      </c>
+      <c r="J15" t="str">
         <v/>
       </c>
     </row>
@@ -753,21 +888,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>CG Power and Industrial Solutions Ltd</v>
+        <v>Siemens Limited</v>
       </c>
       <c r="C16" t="str">
-        <v>CGPOWER</v>
+        <v>SIEMENS</v>
       </c>
       <c r="D16" s="1">
-        <v>867.3</v>
+        <v>3742</v>
       </c>
       <c r="E16" s="2">
-        <v>1.37</v>
+        <v>2.41</v>
       </c>
       <c r="F16" s="1">
-        <v>669763</v>
-      </c>
-      <c r="G16" t="str">
+        <v>107611</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3523.86</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3726.96</v>
+      </c>
+      <c r="I16" s="1">
+        <v>3900.83</v>
+      </c>
+      <c r="J16" t="str">
         <v/>
       </c>
     </row>
@@ -776,21 +920,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Bharat Heavy Electricals Limited</v>
+        <v>Hindustan Aeronautics Ltd</v>
       </c>
       <c r="C17" t="str">
-        <v>BHEL</v>
+        <v>HAL</v>
       </c>
       <c r="D17" s="1">
-        <v>439.45</v>
+        <v>4869</v>
       </c>
       <c r="E17" s="2">
-        <v>1.35</v>
+        <v>2.29</v>
       </c>
       <c r="F17" s="1">
-        <v>3376619</v>
-      </c>
-      <c r="G17" t="str">
+        <v>593863</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4424.09</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4742.54</v>
+      </c>
+      <c r="I17" s="1">
+        <v>4834.2</v>
+      </c>
+      <c r="J17" t="str">
         <v/>
       </c>
     </row>
@@ -799,21 +952,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Anand Rathi Wealth Ltd</v>
+        <v>Dlf Limited</v>
       </c>
       <c r="C18" t="str">
-        <v>ANANDRATHI</v>
+        <v>DLF</v>
       </c>
       <c r="D18" s="1">
-        <v>2065.3</v>
+        <v>664.8</v>
       </c>
       <c r="E18" s="2">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="F18" s="1">
-        <v>476701</v>
-      </c>
-      <c r="G18" t="str">
+        <v>2021831</v>
+      </c>
+      <c r="G18" s="1">
+        <v>627.17</v>
+      </c>
+      <c r="H18" s="1">
+        <v>657.27</v>
+      </c>
+      <c r="I18" s="1">
+        <v>662.89</v>
+      </c>
+      <c r="J18" t="str">
         <v/>
       </c>
     </row>
@@ -822,21 +984,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Multi Commodity Exchange Of India Limited</v>
+        <v>Manappuram Finance Limited</v>
       </c>
       <c r="C19" t="str">
-        <v>MCX</v>
+        <v>MANAPPURAM</v>
       </c>
       <c r="D19" s="1">
-        <v>3360.2</v>
+        <v>326.75</v>
       </c>
       <c r="E19" s="2">
-        <v>1.27</v>
+        <v>2.11</v>
       </c>
       <c r="F19" s="1">
-        <v>709642</v>
-      </c>
-      <c r="G19" t="str">
+        <v>2205945</v>
+      </c>
+      <c r="G19" s="1">
+        <v>310.73</v>
+      </c>
+      <c r="H19" s="1">
+        <v>316.55</v>
+      </c>
+      <c r="I19" s="1">
+        <v>335.97</v>
+      </c>
+      <c r="J19" t="str">
         <v/>
       </c>
     </row>
@@ -845,21 +1016,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>BSE (Bombay stock exchange) Ltd</v>
+        <v>Pnb Housing Finance Limited</v>
       </c>
       <c r="C20" t="str">
-        <v>BSE</v>
+        <v>PNBHOUSING</v>
       </c>
       <c r="D20" s="1">
-        <v>3325.9</v>
+        <v>1224.8</v>
       </c>
       <c r="E20" s="2">
-        <v>1.18</v>
+        <v>2.07</v>
       </c>
       <c r="F20" s="1">
-        <v>1513355</v>
-      </c>
-      <c r="G20" t="str">
+        <v>1027134</v>
+      </c>
+      <c r="G20" s="1">
+        <v>998.28</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1155.31</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1144.49</v>
+      </c>
+      <c r="J20" t="str">
         <v/>
       </c>
     </row>
@@ -868,21 +1048,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Gail (india) Limited</v>
+        <v>Lodha Developers Ltd</v>
       </c>
       <c r="C21" t="str">
-        <v>GAIL</v>
+        <v>LODHA</v>
       </c>
       <c r="D21" s="1">
-        <v>168.61</v>
+        <v>1091.5</v>
       </c>
       <c r="E21" s="2">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="F21" s="1">
-        <v>1192901</v>
-      </c>
-      <c r="G21" t="str">
+        <v>883141</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1022.74</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1098.91</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1179.21</v>
+      </c>
+      <c r="J21" t="str">
         <v/>
       </c>
     </row>
@@ -891,21 +1080,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Aditya Birla Capital Ltd</v>
+        <v>Titan Company Limited</v>
       </c>
       <c r="C22" t="str">
-        <v>ABCAPITAL</v>
+        <v>TITAN</v>
       </c>
       <c r="D22" s="1">
-        <v>385.15</v>
+        <v>4487</v>
       </c>
       <c r="E22" s="2">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="F22" s="1">
-        <v>918375</v>
-      </c>
-      <c r="G22" t="str">
+        <v>527915</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4422.58</v>
+      </c>
+      <c r="H22" s="1">
+        <v>4515.88</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4900.61</v>
+      </c>
+      <c r="J22" t="str">
         <v/>
       </c>
     </row>
@@ -914,21 +1112,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Mankind Pharma Ltd</v>
+        <v>Samvardhana Motherson International Ltd</v>
       </c>
       <c r="C23" t="str">
-        <v>MANKIND</v>
+        <v>MOTHERSON</v>
       </c>
       <c r="D23" s="1">
-        <v>2395.7</v>
+        <v>160</v>
       </c>
       <c r="E23" s="2">
-        <v>1.15</v>
+        <v>1.92</v>
       </c>
       <c r="F23" s="1">
-        <v>35384</v>
-      </c>
-      <c r="G23" t="str">
+        <v>6251818</v>
+      </c>
+      <c r="G23" s="1">
+        <v>137.27</v>
+      </c>
+      <c r="H23" s="1">
+        <v>158.1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>162.87</v>
+      </c>
+      <c r="J23" t="str">
         <v/>
       </c>
     </row>
@@ -937,21 +1144,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Steel Authority Of India Limited</v>
+        <v>Tvs Motor Company Limited</v>
       </c>
       <c r="C24" t="str">
-        <v>SAIL</v>
+        <v>TVSMOTOR</v>
       </c>
       <c r="D24" s="1">
-        <v>173.52</v>
+        <v>4011.5</v>
       </c>
       <c r="E24" s="2">
-        <v>1.15</v>
+        <v>1.81</v>
       </c>
       <c r="F24" s="1">
-        <v>9004297</v>
-      </c>
-      <c r="G24" t="str">
+        <v>586148</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3772.05</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3980.1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>4208.79</v>
+      </c>
+      <c r="J24" t="str">
         <v/>
       </c>
     </row>
@@ -960,21 +1176,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Samvardhana Motherson International Ltd</v>
+        <v>Abb India Limited</v>
       </c>
       <c r="C25" t="str">
-        <v>MOTHERSON</v>
+        <v>ABB</v>
       </c>
       <c r="D25" s="1">
-        <v>154.61</v>
+        <v>6977.5</v>
       </c>
       <c r="E25" s="2">
-        <v>1.05</v>
+        <v>1.78</v>
       </c>
       <c r="F25" s="1">
-        <v>1547172</v>
-      </c>
-      <c r="G25" t="str">
+        <v>201732</v>
+      </c>
+      <c r="G25" s="1">
+        <v>6611.71</v>
+      </c>
+      <c r="H25" s="1">
+        <v>6922.53</v>
+      </c>
+      <c r="I25" s="1">
+        <v>7317.55</v>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
@@ -983,21 +1208,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>One 97 Communications Ltd</v>
+        <v>The Indian Hotels Company Limited</v>
       </c>
       <c r="C26" t="str">
-        <v>PAYTM</v>
+        <v>INDHOTEL</v>
       </c>
       <c r="D26" s="1">
-        <v>1652.4</v>
+        <v>724.15</v>
       </c>
       <c r="E26" s="2">
-        <v>1</v>
+        <v>1.78</v>
       </c>
       <c r="F26" s="1">
-        <v>644290</v>
-      </c>
-      <c r="G26" t="str">
+        <v>1686055</v>
+      </c>
+      <c r="G26" s="1">
+        <v>688.67</v>
+      </c>
+      <c r="H26" s="1">
+        <v>721.32</v>
+      </c>
+      <c r="I26" s="1">
+        <v>725.72</v>
+      </c>
+      <c r="J26" t="str">
         <v/>
       </c>
     </row>
@@ -1006,21 +1240,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>The Phoenix Mills Limited</v>
+        <v>Motilal Oswal Financial Services Limited</v>
       </c>
       <c r="C27" t="str">
-        <v>PHOENIXLTD</v>
+        <v>MOTILALOFS</v>
       </c>
       <c r="D27" s="1">
-        <v>1831</v>
+        <v>1068.9</v>
       </c>
       <c r="E27" s="2">
-        <v>0.99</v>
+        <v>1.7</v>
       </c>
       <c r="F27" s="1">
-        <v>102884</v>
-      </c>
-      <c r="G27" t="str">
+        <v>544091</v>
+      </c>
+      <c r="G27" s="1">
+        <v>864.65</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1037.59</v>
+      </c>
+      <c r="I27" s="1">
+        <v>988.29</v>
+      </c>
+      <c r="J27" t="str">
         <v/>
       </c>
     </row>
@@ -1029,21 +1272,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Nippon Life India Asset Management Ltd</v>
+        <v>Info Edge (india) Limited</v>
       </c>
       <c r="C28" t="str">
-        <v>NAM-INDIA</v>
+        <v>NAUKRI</v>
       </c>
       <c r="D28" s="1">
-        <v>1054.5</v>
+        <v>1222.6</v>
       </c>
       <c r="E28" s="2">
-        <v>0.91</v>
+        <v>1.55</v>
       </c>
       <c r="F28" s="1">
-        <v>130639</v>
-      </c>
-      <c r="G28" t="str">
+        <v>1459720</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1143.53</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1221.33</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1285.77</v>
+      </c>
+      <c r="J28" t="str">
         <v/>
       </c>
     </row>
@@ -1052,21 +1304,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Sona BLW Precision Forgings Ltd</v>
+        <v>Icici Bank Limited</v>
       </c>
       <c r="C29" t="str">
-        <v>SONACOMS</v>
+        <v>ICICIBANK</v>
       </c>
       <c r="D29" s="1">
-        <v>789.9</v>
+        <v>1360.2</v>
       </c>
       <c r="E29" s="2">
-        <v>0.84</v>
+        <v>1.51</v>
       </c>
       <c r="F29" s="1">
-        <v>289459</v>
-      </c>
-      <c r="G29" t="str">
+        <v>5347633</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1353.15</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1344.27</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1389.02</v>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
@@ -1075,21 +1336,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Trent Limited</v>
+        <v>One 97 Communications Ltd</v>
       </c>
       <c r="C30" t="str">
-        <v>TRENT</v>
+        <v>PAYTM</v>
       </c>
       <c r="D30" s="1">
-        <v>2940.5</v>
+        <v>1715</v>
       </c>
       <c r="E30" s="2">
-        <v>0.76</v>
+        <v>1.48</v>
       </c>
       <c r="F30" s="1">
-        <v>363417</v>
-      </c>
-      <c r="G30" t="str">
+        <v>9175743</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1288.26</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1689.56</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1655.62</v>
+      </c>
+      <c r="J30" t="str">
         <v/>
       </c>
     </row>
@@ -1098,21 +1368,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Solar Industries India Limited</v>
+        <v>BSE (Bombay stock exchange) Ltd</v>
       </c>
       <c r="C31" t="str">
-        <v>SOLARINDS</v>
+        <v>BSE</v>
       </c>
       <c r="D31" s="1">
-        <v>20136</v>
+        <v>3375.4</v>
       </c>
       <c r="E31" s="2">
-        <v>0.68</v>
+        <v>1.36</v>
       </c>
       <c r="F31" s="1">
-        <v>42690</v>
-      </c>
-      <c r="G31" t="str">
+        <v>4092659</v>
+      </c>
+      <c r="G31" s="1">
+        <v>3325.24</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3285.18</v>
+      </c>
+      <c r="I31" s="1">
+        <v>3328.9</v>
+      </c>
+      <c r="J31" t="str">
         <v/>
       </c>
     </row>
@@ -1121,21 +1400,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Bosch Limited</v>
+        <v>Adani Energy Solutions Ltd</v>
       </c>
       <c r="C32" t="str">
-        <v>BOSCHLTD</v>
+        <v>ADANIENSOL</v>
       </c>
       <c r="D32" s="1">
-        <v>43810</v>
+        <v>1296.9</v>
       </c>
       <c r="E32" s="2">
-        <v>0.61</v>
+        <v>1.32</v>
       </c>
       <c r="F32" s="1">
-        <v>4632</v>
-      </c>
-      <c r="G32" t="str">
+        <v>632449</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1293.72</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1304.79</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1453.23</v>
+      </c>
+      <c r="J32" t="str">
         <v/>
       </c>
     </row>
@@ -1144,21 +1432,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>Lic Housing Finance Limited</v>
+        <v>Apl Apollo Tubes Limited</v>
       </c>
       <c r="C33" t="str">
-        <v>LICHSGFIN</v>
+        <v>APLAPOLLO</v>
       </c>
       <c r="D33" s="1">
-        <v>555</v>
+        <v>2185</v>
       </c>
       <c r="E33" s="2">
-        <v>0.61</v>
+        <v>1.28</v>
       </c>
       <c r="F33" s="1">
-        <v>777806</v>
-      </c>
-      <c r="G33" t="str">
+        <v>285082</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1998.05</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2144.99</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2131.85</v>
+      </c>
+      <c r="J33" t="str">
         <v/>
       </c>
     </row>
@@ -1167,21 +1464,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Interglobe Aviation Limited</v>
+        <v>Oberoi Realty Limited</v>
       </c>
       <c r="C34" t="str">
-        <v>INDIGO</v>
+        <v>OBEROIRLTY</v>
       </c>
       <c r="D34" s="1">
-        <v>4861.7</v>
+        <v>1720</v>
       </c>
       <c r="E34" s="2">
-        <v>0.59</v>
+        <v>1.18</v>
       </c>
       <c r="F34" s="1">
-        <v>174589</v>
-      </c>
-      <c r="G34" t="str">
+        <v>539677</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1686.01</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1732.01</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1810.88</v>
+      </c>
+      <c r="J34" t="str">
         <v/>
       </c>
     </row>
@@ -1190,21 +1496,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Bajaj Holdings &amp; Investment Limited</v>
+        <v>Aditya Birla Capital Ltd</v>
       </c>
       <c r="C35" t="str">
-        <v>BAJAJHLDNG</v>
+        <v>ABCAPITAL</v>
       </c>
       <c r="D35" s="1">
-        <v>10883</v>
+        <v>384.65</v>
       </c>
       <c r="E35" s="2">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
       <c r="F35" s="1">
-        <v>7420</v>
-      </c>
-      <c r="G35" t="str">
+        <v>4150743</v>
+      </c>
+      <c r="G35" s="1">
+        <v>365.37</v>
+      </c>
+      <c r="H35" s="1">
+        <v>380.5</v>
+      </c>
+      <c r="I35" s="1">
+        <v>398.13</v>
+      </c>
+      <c r="J35" t="str">
         <v/>
       </c>
     </row>
@@ -1213,21 +1528,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Rbl Bank Limited</v>
+        <v>Steel Authority Of India Limited</v>
       </c>
       <c r="C36" t="str">
-        <v>RBLBANK</v>
+        <v>SAIL</v>
       </c>
       <c r="D36" s="1">
-        <v>420.3</v>
+        <v>172.77</v>
       </c>
       <c r="E36" s="2">
-        <v>0.55</v>
+        <v>1.04</v>
       </c>
       <c r="F36" s="1">
-        <v>1282860</v>
-      </c>
-      <c r="G36" t="str">
+        <v>12130310</v>
+      </c>
+      <c r="G36" s="1">
+        <v>169.62</v>
+      </c>
+      <c r="H36" s="1">
+        <v>174.32</v>
+      </c>
+      <c r="I36" s="1">
+        <v>179.62</v>
+      </c>
+      <c r="J36" t="str">
         <v/>
       </c>
     </row>
@@ -1236,21 +1560,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Lodha Developers Ltd</v>
+        <v>Vodafone Idea Ltd</v>
       </c>
       <c r="C37" t="str">
-        <v>LODHA</v>
+        <v>IDEA</v>
       </c>
       <c r="D37" s="1">
-        <v>1070</v>
+        <v>12.8</v>
       </c>
       <c r="E37" s="2">
-        <v>0.49</v>
+        <v>1.03</v>
       </c>
       <c r="F37" s="1">
-        <v>105124</v>
-      </c>
-      <c r="G37" t="str">
+        <v>240202918</v>
+      </c>
+      <c r="G37" s="1">
+        <v>12.29</v>
+      </c>
+      <c r="H37" s="1">
+        <v>13.07</v>
+      </c>
+      <c r="I37" s="1">
+        <v>13.89</v>
+      </c>
+      <c r="J37" t="str">
         <v/>
       </c>
     </row>
@@ -1259,21 +1592,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Oracle Financial Services Software Limited</v>
+        <v>Adani Green Energy Ltd</v>
       </c>
       <c r="C38" t="str">
-        <v>OFSS</v>
+        <v>ADANIGREEN</v>
       </c>
       <c r="D38" s="1">
-        <v>10560</v>
+        <v>1287</v>
       </c>
       <c r="E38" s="2">
-        <v>0.48</v>
+        <v>1.02</v>
       </c>
       <c r="F38" s="1">
-        <v>32788</v>
-      </c>
-      <c r="G38" t="str">
+        <v>1487475</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1205.34</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1280.07</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1305.27</v>
+      </c>
+      <c r="J38" t="str">
         <v/>
       </c>
     </row>
@@ -1282,21 +1624,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Adani Green Energy Ltd</v>
+        <v>Bank Of Maharashtra Ltd</v>
       </c>
       <c r="C39" t="str">
-        <v>ADANIGREEN</v>
+        <v>MAHABANK</v>
       </c>
       <c r="D39" s="1">
-        <v>1261</v>
+        <v>83.74</v>
       </c>
       <c r="E39" s="2">
-        <v>0.41</v>
+        <v>0.89</v>
       </c>
       <c r="F39" s="1">
-        <v>653725</v>
-      </c>
-      <c r="G39" t="str">
+        <v>11424202</v>
+      </c>
+      <c r="G39" s="1">
+        <v>75.71</v>
+      </c>
+      <c r="H39" s="1">
+        <v>82.49</v>
+      </c>
+      <c r="I39" s="1">
+        <v>81.87</v>
+      </c>
+      <c r="J39" t="str">
         <v/>
       </c>
     </row>
@@ -1305,21 +1656,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Adani Enterprises Limited</v>
+        <v>Gail (india) Limited</v>
       </c>
       <c r="C40" t="str">
-        <v>ADANIENT</v>
+        <v>GAIL</v>
       </c>
       <c r="D40" s="1">
-        <v>2642</v>
+        <v>168.3</v>
       </c>
       <c r="E40" s="2">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F40" s="1">
-        <v>413162</v>
-      </c>
-      <c r="G40" t="str">
+        <v>7372415</v>
+      </c>
+      <c r="G40" s="1">
+        <v>166.2</v>
+      </c>
+      <c r="H40" s="1">
+        <v>169.11</v>
+      </c>
+      <c r="I40" s="1">
+        <v>172.87</v>
+      </c>
+      <c r="J40" t="str">
         <v/>
       </c>
     </row>
@@ -1328,21 +1688,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Kalyan Jewellers India Ltd</v>
+        <v>Nippon Life India Asset Management Ltd</v>
       </c>
       <c r="C41" t="str">
-        <v>KALYANKJIL</v>
+        <v>NAM-INDIA</v>
       </c>
       <c r="D41" s="1">
-        <v>555.6</v>
+        <v>1065.7</v>
       </c>
       <c r="E41" s="2">
-        <v>0.29</v>
+        <v>0.82</v>
       </c>
       <c r="F41" s="1">
-        <v>1183623</v>
-      </c>
-      <c r="G41" t="str">
+        <v>540788</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1037.13</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1068.01</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1155.18</v>
+      </c>
+      <c r="J41" t="str">
         <v/>
       </c>
     </row>
@@ -1351,21 +1720,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Laurus Labs Limited</v>
+        <v>Bosch Limited</v>
       </c>
       <c r="C42" t="str">
-        <v>LAURUSLABS</v>
+        <v>BOSCHLTD</v>
       </c>
       <c r="D42" s="1">
-        <v>2041.3</v>
+        <v>44900</v>
       </c>
       <c r="E42" s="2">
-        <v>0.23</v>
+        <v>0.71</v>
       </c>
       <c r="F42" s="1">
-        <v>496299</v>
-      </c>
-      <c r="G42" t="str">
+        <v>16032</v>
+      </c>
+      <c r="G42" s="1">
+        <v>39306.48</v>
+      </c>
+      <c r="H42" s="1">
+        <v>44997.81</v>
+      </c>
+      <c r="I42" s="1">
+        <v>46626.2</v>
+      </c>
+      <c r="J42" t="str">
         <v/>
       </c>
     </row>
@@ -1374,21 +1752,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>Eternal Ltd</v>
+        <v>Kalyan Jewellers India Ltd</v>
       </c>
       <c r="C43" t="str">
-        <v>ETERNAL</v>
+        <v>KALYANKJIL</v>
       </c>
       <c r="D43" s="1">
-        <v>324.2</v>
+        <v>571</v>
       </c>
       <c r="E43" s="2">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="F43" s="1">
-        <v>4172180</v>
-      </c>
-      <c r="G43" t="str">
+        <v>3628708</v>
+      </c>
+      <c r="G43" s="1">
+        <v>463.37</v>
+      </c>
+      <c r="H43" s="1">
+        <v>562.76</v>
+      </c>
+      <c r="I43" s="1">
+        <v>588.61</v>
+      </c>
+      <c r="J43" t="str">
         <v/>
       </c>
     </row>
@@ -1397,21 +1784,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Persistent Systems Limited</v>
+        <v>Dixon Technologies Ltd</v>
       </c>
       <c r="C44" t="str">
-        <v>PERSISTENT</v>
+        <v>DIXON</v>
       </c>
       <c r="D44" s="1">
-        <v>5779.5</v>
+        <v>12740</v>
       </c>
       <c r="E44" s="2">
-        <v>0.16</v>
+        <v>0.63</v>
       </c>
       <c r="F44" s="1">
-        <v>176431</v>
-      </c>
-      <c r="G44" t="str">
+        <v>130453</v>
+      </c>
+      <c r="G44" s="1">
+        <v>12095.57</v>
+      </c>
+      <c r="H44" s="1">
+        <v>12883.54</v>
+      </c>
+      <c r="I44" s="1">
+        <v>13792.04</v>
+      </c>
+      <c r="J44" t="str">
         <v/>
       </c>
     </row>
@@ -1420,21 +1816,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Siemens Energy India Ltd</v>
+        <v>Anand Rathi Wealth Ltd</v>
       </c>
       <c r="C45" t="str">
-        <v>ENRIN</v>
+        <v>ANANDRATHI</v>
       </c>
       <c r="D45" s="1">
-        <v>3104.1</v>
+        <v>2100</v>
       </c>
       <c r="E45" s="2">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="F45" s="1">
-        <v>168986</v>
-      </c>
-      <c r="G45" t="str">
+        <v>241844</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1823.82</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2112.64</v>
+      </c>
+      <c r="I45" s="1">
+        <v>2159.63</v>
+      </c>
+      <c r="J45" t="str">
         <v/>
       </c>
     </row>
@@ -1443,21 +1848,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Divi's Laboratories Limited</v>
+        <v>Sona BLW Precision Forgings Ltd</v>
       </c>
       <c r="C46" t="str">
-        <v>DIVISLAB</v>
+        <v>SONACOMS</v>
       </c>
       <c r="D46" s="1">
-        <v>9338.5</v>
+        <v>802.95</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.02</v>
+        <v>0.62</v>
       </c>
       <c r="F46" s="1">
-        <v>117530</v>
-      </c>
-      <c r="G46" t="str">
+        <v>1989557</v>
+      </c>
+      <c r="G46" s="1">
+        <v>623.47</v>
+      </c>
+      <c r="H46" s="1">
+        <v>802.47</v>
+      </c>
+      <c r="I46" s="1">
+        <v>804.23</v>
+      </c>
+      <c r="J46" t="str">
         <v/>
       </c>
     </row>
@@ -1466,21 +1880,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Dlf Limited</v>
+        <v>Bharat Heavy Electricals Limited</v>
       </c>
       <c r="C47" t="str">
-        <v>DLF</v>
+        <v>BHEL</v>
       </c>
       <c r="D47" s="1">
-        <v>648.35</v>
+        <v>442.35</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.04</v>
+        <v>0.56</v>
       </c>
       <c r="F47" s="1">
-        <v>341508</v>
-      </c>
-      <c r="G47" t="str">
+        <v>15751366</v>
+      </c>
+      <c r="G47" s="1">
+        <v>351.79</v>
+      </c>
+      <c r="H47" s="1">
+        <v>434.47</v>
+      </c>
+      <c r="I47" s="1">
+        <v>423.64</v>
+      </c>
+      <c r="J47" t="str">
         <v/>
       </c>
     </row>
@@ -1489,21 +1912,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Page Industries Limited</v>
+        <v>Bajaj Holdings &amp; Investment Limited</v>
       </c>
       <c r="C48" t="str">
-        <v>PAGEIND</v>
+        <v>BAJAJHLDNG</v>
       </c>
       <c r="D48" s="1">
-        <v>36845</v>
+        <v>10808</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.08</v>
+        <v>0.54</v>
       </c>
       <c r="F48" s="1">
-        <v>1824</v>
-      </c>
-      <c r="G48" t="str">
+        <v>25046</v>
+      </c>
+      <c r="G48" s="1">
+        <v>10668.62</v>
+      </c>
+      <c r="H48" s="1">
+        <v>10771.65</v>
+      </c>
+      <c r="I48" s="1">
+        <v>11156.4</v>
+      </c>
+      <c r="J48" t="str">
         <v/>
       </c>
     </row>
@@ -1512,21 +1944,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Kotak Mahindra Bank Limited</v>
+        <v>Page Industries Limited</v>
       </c>
       <c r="C49" t="str">
-        <v>KOTAKBANK</v>
+        <v>PAGEIND</v>
       </c>
       <c r="D49" s="1">
-        <v>440.65</v>
+        <v>37100</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.08</v>
+        <v>0.53</v>
       </c>
       <c r="F49" s="1">
-        <v>3166965</v>
-      </c>
-      <c r="G49" t="str">
+        <v>13947</v>
+      </c>
+      <c r="G49" s="1">
+        <v>36390.83</v>
+      </c>
+      <c r="H49" s="1">
+        <v>36989.75</v>
+      </c>
+      <c r="I49" s="1">
+        <v>36767.8</v>
+      </c>
+      <c r="J49" t="str">
         <v/>
       </c>
     </row>
@@ -1535,21 +1976,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Oberoi Realty Limited</v>
+        <v>Adani Ports And Special Economic Zone Limited</v>
       </c>
       <c r="C50" t="str">
-        <v>OBEROIRLTY</v>
+        <v>ADANIPORTS</v>
       </c>
       <c r="D50" s="1">
-        <v>1697</v>
+        <v>1763</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
       <c r="F50" s="1">
-        <v>147912</v>
-      </c>
-      <c r="G50" t="str">
+        <v>3404367</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1636.39</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1759.56</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1724.09</v>
+      </c>
+      <c r="J50" t="str">
         <v/>
       </c>
     </row>
@@ -1558,21 +2008,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Info Edge (india) Limited</v>
+        <v>Punjab National Bank Ltd</v>
       </c>
       <c r="C51" t="str">
-        <v>NAUKRI</v>
+        <v>PNB</v>
       </c>
       <c r="D51" s="1">
-        <v>1217.7</v>
+        <v>116.55</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.11</v>
+        <v>0.47</v>
       </c>
       <c r="F51" s="1">
-        <v>99544</v>
-      </c>
-      <c r="G51" t="str">
+        <v>10380453</v>
+      </c>
+      <c r="G51" s="1">
+        <v>114.26</v>
+      </c>
+      <c r="H51" s="1">
+        <v>115.06</v>
+      </c>
+      <c r="I51" s="1">
+        <v>115.61</v>
+      </c>
+      <c r="J51" t="str">
         <v/>
       </c>
     </row>
@@ -1581,21 +2040,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Aurobindo Pharma Limited</v>
+        <v>The Federal Bank  Limited</v>
       </c>
       <c r="C52" t="str">
-        <v>AUROPHARMA</v>
+        <v>FEDERALBNK</v>
       </c>
       <c r="D52" s="1">
-        <v>1689.9</v>
+        <v>329.5</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="F52" s="1">
-        <v>378540</v>
-      </c>
-      <c r="G52" t="str">
+        <v>2520741</v>
+      </c>
+      <c r="G52" s="1">
+        <v>306.23</v>
+      </c>
+      <c r="H52" s="1">
+        <v>326.28</v>
+      </c>
+      <c r="I52" s="1">
+        <v>342.42</v>
+      </c>
+      <c r="J52" t="str">
         <v/>
       </c>
     </row>
@@ -1604,21 +2072,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>IDFC First Bank Ltd</v>
+        <v>Siemens Energy India Ltd</v>
       </c>
       <c r="C53" t="str">
-        <v>IDFCFIRSTB</v>
+        <v>ENRIN</v>
       </c>
       <c r="D53" s="1">
-        <v>79.35</v>
+        <v>3123.3</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.21</v>
+        <v>0.17</v>
       </c>
       <c r="F53" s="1">
-        <v>3488171</v>
-      </c>
-      <c r="G53" t="str">
+        <v>309455</v>
+      </c>
+      <c r="G53" s="1">
+        <v>3089.94</v>
+      </c>
+      <c r="H53" s="1">
+        <v>3191.99</v>
+      </c>
+      <c r="I53" s="1">
+        <v>3288.86</v>
+      </c>
+      <c r="J53" t="str">
         <v/>
       </c>
     </row>
@@ -1627,21 +2104,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Radico Khaitan Limited</v>
+        <v>Zydus Lifesciences Ltd</v>
       </c>
       <c r="C54" t="str">
-        <v>RADICO</v>
+        <v>ZYDUSLIFE</v>
       </c>
       <c r="D54" s="1">
-        <v>4537.1</v>
+        <v>1132.5</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="F54" s="1">
-        <v>68451</v>
-      </c>
-      <c r="G54" t="str">
+        <v>1098007</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1018.68</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1141.76</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1144.26</v>
+      </c>
+      <c r="J54" t="str">
         <v/>
       </c>
     </row>
@@ -1650,21 +2136,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>The Indian Hotels Company Limited</v>
+        <v>Petronet Lng Limited</v>
       </c>
       <c r="C55" t="str">
-        <v>INDHOTEL</v>
+        <v>PETRONET</v>
       </c>
       <c r="D55" s="1">
-        <v>713.5</v>
+        <v>290</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.3</v>
+        <v>-0.17</v>
       </c>
       <c r="F55" s="1">
-        <v>208021</v>
-      </c>
-      <c r="G55" t="str">
+        <v>1261523</v>
+      </c>
+      <c r="G55" s="1">
+        <v>282.06</v>
+      </c>
+      <c r="H55" s="1">
+        <v>290.16</v>
+      </c>
+      <c r="I55" s="1">
+        <v>287.29</v>
+      </c>
+      <c r="J55" t="str">
         <v/>
       </c>
     </row>
@@ -1673,21 +2168,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>Petronet Lng Limited</v>
+        <v>Radico Khaitan Limited</v>
       </c>
       <c r="C56" t="str">
-        <v>PETRONET</v>
+        <v>RADICO</v>
       </c>
       <c r="D56" s="1">
-        <v>290.45</v>
+        <v>4540</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="F56" s="1">
-        <v>452528</v>
-      </c>
-      <c r="G56" t="str">
+        <v>96820</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3571.78</v>
+      </c>
+      <c r="H56" s="1">
+        <v>4477</v>
+      </c>
+      <c r="I56" s="1">
+        <v>4512.28</v>
+      </c>
+      <c r="J56" t="str">
         <v/>
       </c>
     </row>
@@ -1696,21 +2200,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Bank Of Maharashtra Ltd</v>
+        <v>Laurus Labs Limited</v>
       </c>
       <c r="C57" t="str">
-        <v>MAHABANK</v>
+        <v>LAURUSLABS</v>
       </c>
       <c r="D57" s="1">
-        <v>82.86</v>
+        <v>2059.4</v>
       </c>
       <c r="E57" s="2">
-        <v>-0.36</v>
+        <v>-0.47</v>
       </c>
       <c r="F57" s="1">
-        <v>3166707</v>
-      </c>
-      <c r="G57" t="str">
+        <v>1103307</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1388.72</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2027.89</v>
+      </c>
+      <c r="I57" s="1">
+        <v>1917.73</v>
+      </c>
+      <c r="J57" t="str">
         <v/>
       </c>
     </row>
@@ -1719,21 +2232,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>The Federal Bank  Limited</v>
+        <v>FSN E-Commerce Ventures Ltd</v>
       </c>
       <c r="C58" t="str">
-        <v>FEDERALBNK</v>
+        <v>NYKAA</v>
       </c>
       <c r="D58" s="1">
-        <v>328.55</v>
+        <v>338</v>
       </c>
       <c r="E58" s="2">
-        <v>-0.44</v>
+        <v>-0.59</v>
       </c>
       <c r="F58" s="1">
-        <v>1109248</v>
-      </c>
-      <c r="G58" t="str">
+        <v>6970466</v>
+      </c>
+      <c r="G58" s="1">
+        <v>287.26</v>
+      </c>
+      <c r="H58" s="1">
+        <v>336.51</v>
+      </c>
+      <c r="I58" s="1">
+        <v>334.11</v>
+      </c>
+      <c r="J58" t="str">
         <v/>
       </c>
     </row>
@@ -1742,21 +2264,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Adani Ports And Special Economic Zone Limited</v>
+        <v>Lic Housing Finance Limited</v>
       </c>
       <c r="C59" t="str">
-        <v>ADANIPORTS</v>
+        <v>LICHSGFIN</v>
       </c>
       <c r="D59" s="1">
-        <v>1752.9</v>
+        <v>564</v>
       </c>
       <c r="E59" s="2">
-        <v>-0.46</v>
+        <v>-0.7</v>
       </c>
       <c r="F59" s="1">
-        <v>630980</v>
-      </c>
-      <c r="G59" t="str">
+        <v>1798378</v>
+      </c>
+      <c r="G59" s="1">
+        <v>533.58</v>
+      </c>
+      <c r="H59" s="1">
+        <v>544.48</v>
+      </c>
+      <c r="I59" s="1">
+        <v>531.62</v>
+      </c>
+      <c r="J59" t="str">
         <v/>
       </c>
     </row>
@@ -1765,21 +2296,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Dixon Technologies Ltd</v>
+        <v>IDFC First Bank Ltd</v>
       </c>
       <c r="C60" t="str">
-        <v>DIXON</v>
+        <v>IDFCFIRSTB</v>
       </c>
       <c r="D60" s="1">
-        <v>12695</v>
+        <v>78.83</v>
       </c>
       <c r="E60" s="2">
-        <v>-0.62</v>
+        <v>-0.77</v>
       </c>
       <c r="F60" s="1">
-        <v>67281</v>
-      </c>
-      <c r="G60" t="str">
+        <v>9503151</v>
+      </c>
+      <c r="G60" s="1">
+        <v>77.59</v>
+      </c>
+      <c r="H60" s="1">
+        <v>80.34</v>
+      </c>
+      <c r="I60" s="1">
+        <v>84.34</v>
+      </c>
+      <c r="J60" t="str">
         <v/>
       </c>
     </row>
@@ -1788,21 +2328,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Zydus Lifesciences Ltd</v>
+        <v>Glenmark Pharmaceuticals Limited</v>
       </c>
       <c r="C61" t="str">
-        <v>ZYDUSLIFE</v>
+        <v>GLENMARK</v>
       </c>
       <c r="D61" s="1">
-        <v>1110</v>
+        <v>2265.3</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.67</v>
+        <v>-0.78</v>
       </c>
       <c r="F61" s="1">
-        <v>152023</v>
-      </c>
-      <c r="G61" t="str">
+        <v>249715</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2211.14</v>
+      </c>
+      <c r="H61" s="1">
+        <v>2300.32</v>
+      </c>
+      <c r="I61" s="1">
+        <v>2363.06</v>
+      </c>
+      <c r="J61" t="str">
         <v/>
       </c>
     </row>
@@ -1811,21 +2360,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Torrent Pharmaceuticals Limited</v>
+        <v>Eternal Ltd</v>
       </c>
       <c r="C62" t="str">
-        <v>TORNTPHARM</v>
+        <v>ETERNAL</v>
       </c>
       <c r="D62" s="1">
-        <v>4619.7</v>
+        <v>320.45</v>
       </c>
       <c r="E62" s="2">
-        <v>-0.8</v>
+        <v>-0.79</v>
       </c>
       <c r="F62" s="1">
-        <v>121121</v>
-      </c>
-      <c r="G62" t="str">
+        <v>18081964</v>
+      </c>
+      <c r="G62" s="1">
+        <v>277.88</v>
+      </c>
+      <c r="H62" s="1">
+        <v>323.71</v>
+      </c>
+      <c r="I62" s="1">
+        <v>323.26</v>
+      </c>
+      <c r="J62" t="str">
         <v/>
       </c>
     </row>
@@ -1834,21 +2392,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Glenmark Pharmaceuticals Limited</v>
+        <v>Torrent Pharmaceuticals Limited</v>
       </c>
       <c r="C63" t="str">
-        <v>GLENMARK</v>
+        <v>TORNTPHARM</v>
       </c>
       <c r="D63" s="1">
-        <v>2268.4</v>
+        <v>4642.9</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.07</v>
+        <v>-0.84</v>
       </c>
       <c r="F63" s="1">
-        <v>136893</v>
-      </c>
-      <c r="G63" t="str">
+        <v>161209</v>
+      </c>
+      <c r="G63" s="1">
+        <v>4468.17</v>
+      </c>
+      <c r="H63" s="1">
+        <v>4726.04</v>
+      </c>
+      <c r="I63" s="1">
+        <v>4896.66</v>
+      </c>
+      <c r="J63" t="str">
         <v/>
       </c>
     </row>
@@ -1857,21 +2424,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>FSN E-Commerce Ventures Ltd</v>
+        <v>Kotak Mahindra Bank Limited</v>
       </c>
       <c r="C64" t="str">
-        <v>NYKAA</v>
+        <v>KOTAKBANK</v>
       </c>
       <c r="D64" s="1">
-        <v>339.1</v>
+        <v>439</v>
       </c>
       <c r="E64" s="2">
-        <v>-1.14</v>
+        <v>-0.99</v>
       </c>
       <c r="F64" s="1">
-        <v>962612</v>
-      </c>
-      <c r="G64" t="str">
+        <v>20141914</v>
+      </c>
+      <c r="G64" s="1">
+        <v>399.97</v>
+      </c>
+      <c r="H64" s="1">
+        <v>431.17</v>
+      </c>
+      <c r="I64" s="1">
+        <v>411.53</v>
+      </c>
+      <c r="J64" t="str">
         <v/>
       </c>
     </row>
@@ -1880,21 +2456,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Coforge (Niit Tech) Ltd</v>
+        <v>Ather Energy Ltd</v>
       </c>
       <c r="C65" t="str">
-        <v>COFORGE</v>
+        <v>ATHERENERG</v>
       </c>
       <c r="D65" s="1">
-        <v>1846.4</v>
+        <v>1494.9</v>
       </c>
       <c r="E65" s="2">
-        <v>-1.15</v>
+        <v>-1.07</v>
       </c>
       <c r="F65" s="1">
-        <v>411646</v>
-      </c>
-      <c r="G65" t="str">
+        <v>2197600</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1032.09</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1465.58</v>
+      </c>
+      <c r="I65" s="1">
+        <v>1515.19</v>
+      </c>
+      <c r="J65" t="str">
         <v/>
       </c>
     </row>
@@ -1903,21 +2488,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Punjab National Bank Ltd</v>
+        <v>Mankind Pharma Ltd</v>
       </c>
       <c r="C66" t="str">
-        <v>PNB</v>
+        <v>MANKIND</v>
       </c>
       <c r="D66" s="1">
-        <v>115.34</v>
+        <v>2372</v>
       </c>
       <c r="E66" s="2">
-        <v>-1.4</v>
+        <v>-1.17</v>
       </c>
       <c r="F66" s="1">
-        <v>3498675</v>
-      </c>
-      <c r="G66" t="str">
+        <v>317034</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2303.83</v>
+      </c>
+      <c r="H66" s="1">
+        <v>2424.31</v>
+      </c>
+      <c r="I66" s="1">
+        <v>2399.88</v>
+      </c>
+      <c r="J66" t="str">
         <v/>
       </c>
     </row>
@@ -1926,27 +2520,260 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Vodafone Idea Ltd</v>
+        <v>Solar Industries India Limited</v>
       </c>
       <c r="C67" t="str">
-        <v>IDEA</v>
+        <v>SOLARINDS</v>
       </c>
       <c r="D67" s="1">
-        <v>12.72</v>
+        <v>20087</v>
       </c>
       <c r="E67" s="2">
-        <v>-2.15</v>
+        <v>-1.21</v>
       </c>
       <c r="F67" s="1">
-        <v>163888675</v>
-      </c>
-      <c r="G67" t="str">
+        <v>94649</v>
+      </c>
+      <c r="G67" s="1">
+        <v>16494.38</v>
+      </c>
+      <c r="H67" s="1">
+        <v>19916.49</v>
+      </c>
+      <c r="I67" s="1">
+        <v>19911.92</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Aurobindo Pharma Limited</v>
+      </c>
+      <c r="C68" t="str">
+        <v>AUROPHARMA</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1684.6</v>
+      </c>
+      <c r="E68" s="2">
+        <v>-1.31</v>
+      </c>
+      <c r="F68" s="1">
+        <v>913722</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1431.92</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1686.49</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1661.35</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>GE Vernova T&amp;D India Ltd</v>
+      </c>
+      <c r="C69" t="str">
+        <v>GVT&amp;D</v>
+      </c>
+      <c r="D69" s="1">
+        <v>4191.2</v>
+      </c>
+      <c r="E69" s="2">
+        <v>-1.48</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1076515</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4100.54</v>
+      </c>
+      <c r="H69" s="1">
+        <v>4238.04</v>
+      </c>
+      <c r="I69" s="1">
+        <v>4314.73</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Divi's Laboratories Limited</v>
+      </c>
+      <c r="C70" t="str">
+        <v>DIVISLAB</v>
+      </c>
+      <c r="D70" s="1">
+        <v>9285</v>
+      </c>
+      <c r="E70" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="F70" s="1">
+        <v>408297</v>
+      </c>
+      <c r="G70" s="1">
+        <v>7142.92</v>
+      </c>
+      <c r="H70" s="1">
+        <v>9385.47</v>
+      </c>
+      <c r="I70" s="1">
+        <v>9061.23</v>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>CG Power and Industrial Solutions Ltd</v>
+      </c>
+      <c r="C71" t="str">
+        <v>CGPOWER</v>
+      </c>
+      <c r="D71" s="1">
+        <v>854</v>
+      </c>
+      <c r="E71" s="2">
+        <v>-1.56</v>
+      </c>
+      <c r="F71" s="1">
+        <v>2439898</v>
+      </c>
+      <c r="G71" s="1">
+        <v>800.27</v>
+      </c>
+      <c r="H71" s="1">
+        <v>871.24</v>
+      </c>
+      <c r="I71" s="1">
+        <v>882.87</v>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Multi Commodity Exchange Of India Limited</v>
+      </c>
+      <c r="C72" t="str">
+        <v>MCX</v>
+      </c>
+      <c r="D72" s="1">
+        <v>3308</v>
+      </c>
+      <c r="E72" s="2">
+        <v>-2.42</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1632955</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2787.41</v>
+      </c>
+      <c r="H72" s="1">
+        <v>3305.43</v>
+      </c>
+      <c r="I72" s="1">
+        <v>3162.63</v>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Hitachi Energy India Ltd</v>
+      </c>
+      <c r="C73" t="str">
+        <v>POWERINDIA</v>
+      </c>
+      <c r="D73" s="1">
+        <v>30250</v>
+      </c>
+      <c r="E73" s="2">
+        <v>-3.32</v>
+      </c>
+      <c r="F73" s="1">
+        <v>197422</v>
+      </c>
+      <c r="G73" s="1">
+        <v>28812.61</v>
+      </c>
+      <c r="H73" s="1">
+        <v>30981.42</v>
+      </c>
+      <c r="I73" s="1">
+        <v>32394.7</v>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Rbl Bank Limited</v>
+      </c>
+      <c r="C74" t="str">
+        <v>RBLBANK</v>
+      </c>
+      <c r="D74" s="1">
+        <v>388.05</v>
+      </c>
+      <c r="E74" s="2">
+        <v>-7.1</v>
+      </c>
+      <c r="F74" s="1">
+        <v>39111672</v>
+      </c>
+      <c r="G74" s="1">
+        <v>346.64</v>
+      </c>
+      <c r="H74" s="1">
+        <v>407.88</v>
+      </c>
+      <c r="I74" s="1">
+        <v>399.47</v>
+      </c>
+      <c r="J74" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J74"/>
   </ignoredErrors>
 </worksheet>
 </file>